--- a/Partial/PriceVolDefinition/PriceVolGain Excel Simulation/Simulation PriceVolGain.xlsx
+++ b/Partial/PriceVolDefinition/PriceVolGain Excel Simulation/Simulation PriceVolGain.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdufour\Documents\MDWork\YahooAccess\YahooAccessData VS2012\Partial\PriceVolDefinition\PriceVolGain Excel Simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE4D72B-55E2-4CD4-9DCE-ADC3FC9BB6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09E962CC-27FE-41DB-98EB-A3CBC21E31B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="27493" windowHeight="13866" xr2:uid="{C4E7A5FC-5097-4192-8A38-10EEA9F44E4B}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="12432" xr2:uid="{C4E7A5FC-5097-4192-8A38-10EEA9F44E4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,16 +443,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C524C52-552E-4096-85E7-A3517836E4F6}">
-  <dimension ref="A1:O50"/>
-  <sheetFormatPr defaultRowHeight="13.7"/>
+  <dimension ref="A1:M50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="12.38671875" customWidth="1"/>
-    <col min="5" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.38671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.609375" customWidth="1"/>
+    <col min="1" max="2" width="12.3671875" customWidth="1"/>
+    <col min="5" max="5" width="23.15625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.3671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.62890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -471,77 +471,77 @@
       <c r="F1" t="s">
         <v>4</v>
       </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
       <c r="J1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1" t="s">
-        <v>2</v>
-      </c>
-      <c r="N1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <f>J$2</f>
+        <v>100</v>
+      </c>
+      <c r="B2">
+        <f>K$2</f>
+        <v>400</v>
+      </c>
+      <c r="C2">
+        <f>LN(A2/J$2)</f>
         <v>0</v>
       </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2">
-        <f>L$2</f>
+      <c r="D2">
+        <f>LN(B2/K$2)</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>50*EXP(C2-C$10)</f>
+        <v>46.174161124115606</v>
+      </c>
+      <c r="F2">
+        <f>50*EXP(D2-D$10)</f>
+        <v>42.674518559505572</v>
+      </c>
+      <c r="H2">
+        <v>0.01</v>
+      </c>
+      <c r="I2">
+        <v>0.02</v>
+      </c>
+      <c r="J2">
         <v>100</v>
       </c>
-      <c r="B2">
-        <f>M$2</f>
-        <v>300</v>
-      </c>
-      <c r="C2">
-        <f>LN(A2/L$2)</f>
+      <c r="K2">
+        <v>400</v>
+      </c>
+      <c r="L2">
+        <v>50</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>LN(B2/M$2)</f>
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>C2+$N$2</f>
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <f>D2+$N$2</f>
-        <v>50</v>
-      </c>
-      <c r="J2">
-        <v>0.01</v>
-      </c>
-      <c r="K2">
-        <v>0.01</v>
-      </c>
-      <c r="L2">
-        <v>100</v>
-      </c>
-      <c r="M2">
-        <v>300</v>
-      </c>
-      <c r="N2">
-        <v>50</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
-        <f>A2+J$2*A2</f>
+        <f>A2+H$2*A2</f>
         <v>101</v>
       </c>
       <c r="B3">
-        <f>B2+K$2*B2</f>
-        <v>303</v>
+        <f>B2+I$2*B2</f>
+        <v>408</v>
       </c>
       <c r="C3">
         <f>LN(A3/A2)+C2</f>
@@ -549,1341 +549,1237 @@
       </c>
       <c r="D3">
         <f>LN(B3/B2)+D2</f>
-        <v>9.950330853168092E-3</v>
+        <v>1.980262729617973E-2</v>
       </c>
       <c r="E3">
-        <f>C3+$N$2</f>
-        <v>50.009950330853165</v>
+        <f t="shared" ref="E3:E50" si="0">50*EXP(C3-C$10)</f>
+        <v>46.635902735356765</v>
       </c>
       <c r="F3">
-        <f>D3+$N$2</f>
-        <v>50.009950330853165</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G13" si="0">LN(A3/A$2)</f>
-        <v>9.950330853168092E-3</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H13" si="1">LN(B3/B$2)</f>
-        <v>9.950330853168092E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <f t="shared" ref="F3:F50" si="1">50*EXP(D3-D$10)</f>
+        <v>43.528008930695684</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
-        <f t="shared" ref="A4:A50" si="2">A3+J$2*A3</f>
+        <f>A3+H$2*A3</f>
         <v>102.01</v>
       </c>
       <c r="B4">
-        <f t="shared" ref="B4:B50" si="3">B3+K$2*B3</f>
-        <v>306.02999999999997</v>
+        <f>B3+I$2*B3</f>
+        <v>416.16</v>
       </c>
       <c r="C4">
-        <f t="shared" ref="C4:C50" si="4">LN(A4/A3)+C3</f>
+        <f t="shared" ref="C4:C50" si="2">LN(A4/A3)+C3</f>
         <v>1.9900661706336184E-2</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D50" si="5">LN(B4/B3)+D3</f>
-        <v>1.9900661706336184E-2</v>
+        <f t="shared" ref="D4:D50" si="3">LN(B4/B3)+D3</f>
+        <v>3.960525459235946E-2</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E50" si="6">$C4+N$2</f>
-        <v>50.019900661706338</v>
+        <f t="shared" si="0"/>
+        <v>47.102261762710334</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F50" si="7">D4+$N$2</f>
-        <v>50.019900661706338</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>1.9900661706336174E-2</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="1"/>
-        <v>1.9900661706336174E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>44.398569109309598</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
-        <f t="shared" si="2"/>
+        <f>A4+H$2*A4</f>
         <v>103.0301</v>
       </c>
       <c r="B5">
-        <f t="shared" si="3"/>
-        <v>309.09029999999996</v>
+        <f>B4+I$2*B4</f>
+        <v>424.48320000000001</v>
       </c>
       <c r="C5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>2.9850992559504276E-2</v>
       </c>
       <c r="D5">
-        <f t="shared" si="5"/>
-        <v>2.9850992559504276E-2</v>
+        <f t="shared" si="3"/>
+        <v>5.9407881888539189E-2</v>
       </c>
       <c r="E5">
-        <f t="shared" si="6"/>
-        <v>50.029850992559503</v>
+        <f t="shared" si="0"/>
+        <v>47.573284380337441</v>
       </c>
       <c r="F5">
-        <f t="shared" si="7"/>
-        <v>50.029850992559503</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>2.9850992559504377E-2</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="1"/>
-        <v>2.9850992559504162E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>45.286540491495792</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
-        <f t="shared" si="2"/>
+        <f>A5+H$2*A5</f>
         <v>104.060401</v>
       </c>
       <c r="B6">
-        <f t="shared" si="3"/>
-        <v>312.18120299999998</v>
+        <f>B5+I$2*B5</f>
+        <v>432.97286400000002</v>
       </c>
       <c r="C6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>3.9801323412672368E-2</v>
       </c>
       <c r="D6">
-        <f t="shared" si="5"/>
-        <v>3.9801323412672368E-2</v>
+        <f t="shared" si="3"/>
+        <v>7.9210509184718919E-2</v>
       </c>
       <c r="E6">
-        <f t="shared" si="6"/>
-        <v>50.039801323412675</v>
+        <f t="shared" si="0"/>
+        <v>48.049017224140812</v>
       </c>
       <c r="F6">
-        <f t="shared" si="7"/>
-        <v>50.039801323412675</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>3.9801323412672354E-2</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="1"/>
-        <v>3.9801323412672354E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>46.192271301325704</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
-        <f t="shared" si="2"/>
+        <f>A6+H$2*A6</f>
         <v>105.10100500999999</v>
       </c>
       <c r="B7">
-        <f t="shared" si="3"/>
-        <v>315.30301502999998</v>
+        <f>B6+I$2*B6</f>
+        <v>441.63232128000004</v>
       </c>
       <c r="C7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>4.975165426584046E-2</v>
       </c>
       <c r="D7">
-        <f t="shared" si="5"/>
-        <v>4.975165426584046E-2</v>
+        <f t="shared" si="3"/>
+        <v>9.9013136480898656E-2</v>
       </c>
       <c r="E7">
-        <f t="shared" si="6"/>
-        <v>50.04975165426584</v>
+        <f t="shared" si="0"/>
+        <v>48.529507396382222</v>
       </c>
       <c r="F7">
-        <f t="shared" si="7"/>
-        <v>50.04975165426584</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="0"/>
-        <v>4.9751654265840342E-2</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="1"/>
-        <v>4.9751654265840342E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>47.116116727352221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
-        <f t="shared" si="2"/>
+        <f>A7+H$2*A7</f>
         <v>106.1520150601</v>
       </c>
       <c r="B8">
-        <f t="shared" si="3"/>
-        <v>318.45604518030001</v>
+        <f>B7+I$2*B7</f>
+        <v>450.46496770560003</v>
       </c>
       <c r="C8">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>5.9701985119008552E-2</v>
       </c>
       <c r="D8">
-        <f t="shared" si="5"/>
-        <v>5.9701985119008552E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.11881576377707839</v>
       </c>
       <c r="E8">
-        <f t="shared" si="6"/>
-        <v>50.059701985119005</v>
+        <f t="shared" si="0"/>
+        <v>49.014802470346041</v>
       </c>
       <c r="F8">
-        <f t="shared" si="7"/>
-        <v>50.059701985119005</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="0"/>
-        <v>5.9701985119008413E-2</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="1"/>
-        <v>5.9701985119008621E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>48.058439061899264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
-        <f t="shared" si="2"/>
+        <f>A8+H$2*A8</f>
         <v>107.213535210701</v>
       </c>
       <c r="B9">
-        <f t="shared" si="3"/>
-        <v>321.64060563210302</v>
+        <f>B8+I$2*B8</f>
+        <v>459.47426705971202</v>
       </c>
       <c r="C9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>6.9652315972176637E-2</v>
       </c>
       <c r="D9">
-        <f t="shared" si="5"/>
-        <v>6.9652315972176637E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.13861839107325813</v>
       </c>
       <c r="E9">
-        <f t="shared" si="6"/>
-        <v>50.069652315972178</v>
+        <f t="shared" si="0"/>
+        <v>49.504950495049506</v>
       </c>
       <c r="F9">
-        <f t="shared" si="7"/>
-        <v>50.069652315972178</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>6.9652315972176623E-2</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="1"/>
-        <v>6.9652315972176623E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>49.019607843137251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
-        <f t="shared" si="2"/>
+        <f>A9+H$2*A9</f>
         <v>108.28567056280801</v>
       </c>
       <c r="B10">
-        <f t="shared" si="3"/>
-        <v>324.85701168842405</v>
+        <f>B9+I$2*B9</f>
+        <v>468.66375240090628</v>
       </c>
       <c r="C10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>7.9602646825344736E-2</v>
       </c>
       <c r="D10">
-        <f t="shared" si="5"/>
-        <v>7.9602646825344736E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.15842101836943787</v>
       </c>
       <c r="E10">
-        <f t="shared" si="6"/>
-        <v>50.079602646825343</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="F10">
-        <f t="shared" si="7"/>
-        <v>50.079602646825343</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="0"/>
-        <v>7.9602646825344583E-2</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="1"/>
-        <v>7.9602646825344778E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
-        <f t="shared" si="2"/>
+        <f>A10+H$2*A10</f>
         <v>109.36852726843608</v>
       </c>
       <c r="B11">
-        <f t="shared" si="3"/>
-        <v>328.1055818053083</v>
+        <f>B10+I$2*B10</f>
+        <v>478.03702744892439</v>
       </c>
       <c r="C11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>8.9552977678512835E-2</v>
       </c>
       <c r="D11">
-        <f t="shared" si="5"/>
-        <v>8.9552977678512835E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.1782236456656176</v>
       </c>
       <c r="E11">
-        <f t="shared" si="6"/>
-        <v>50.089552977678515</v>
+        <f t="shared" si="0"/>
+        <v>50.5</v>
       </c>
       <c r="F11">
-        <f t="shared" si="7"/>
-        <v>50.089552977678515</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="0"/>
-        <v>8.9552977678512738E-2</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="1"/>
-        <v>8.9552977678512932E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <f t="shared" si="2"/>
+        <f>A11+H$2*A11</f>
         <v>110.46221254112044</v>
       </c>
       <c r="B12">
-        <f t="shared" si="3"/>
-        <v>331.38663762336137</v>
+        <f>B11+I$2*B11</f>
+        <v>487.59776799790291</v>
       </c>
       <c r="C12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>9.9503308531680934E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="5"/>
-        <v>9.9503308531680934E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.19802627296179734</v>
       </c>
       <c r="E12">
-        <f t="shared" si="6"/>
-        <v>50.099503308531681</v>
+        <f t="shared" si="0"/>
+        <v>51.005000000000003</v>
       </c>
       <c r="F12">
-        <f t="shared" si="7"/>
-        <v>50.099503308531681</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="0"/>
-        <v>9.9503308531680643E-2</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="1"/>
-        <v>9.9503308531680837E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>52.019999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <f t="shared" si="2"/>
+        <f>A12+H$2*A12</f>
         <v>111.56683466653165</v>
       </c>
       <c r="B13">
-        <f t="shared" si="3"/>
-        <v>334.70050399959496</v>
+        <f>B12+I$2*B12</f>
+        <v>497.34972335786097</v>
       </c>
       <c r="C13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.10945363938484903</v>
       </c>
       <c r="D13">
-        <f t="shared" si="5"/>
-        <v>0.10945363938484903</v>
+        <f t="shared" si="3"/>
+        <v>0.21782890025797708</v>
       </c>
       <c r="E13">
-        <f t="shared" si="6"/>
-        <v>50.109453639384846</v>
+        <f t="shared" si="0"/>
+        <v>51.515050000000009</v>
       </c>
       <c r="F13">
-        <f t="shared" si="7"/>
-        <v>50.109453639384846</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="0"/>
-        <v>0.10945363938484891</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="1"/>
-        <v>0.10945363938484891</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>53.060400000000008</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <f t="shared" si="2"/>
+        <f>A13+H$2*A13</f>
         <v>112.68250301319696</v>
       </c>
       <c r="B14">
-        <f t="shared" si="3"/>
-        <v>338.04750903959092</v>
+        <f>B13+I$2*B13</f>
+        <v>507.29671782501816</v>
       </c>
       <c r="C14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.11940397023801713</v>
       </c>
       <c r="D14">
-        <f t="shared" si="5"/>
-        <v>0.11940397023801713</v>
+        <f t="shared" si="3"/>
+        <v>0.23763152755415681</v>
       </c>
       <c r="E14">
-        <f t="shared" si="6"/>
-        <v>50.119403970238018</v>
+        <f t="shared" si="0"/>
+        <v>52.030200499999999</v>
       </c>
       <c r="F14">
-        <f t="shared" si="7"/>
-        <v>50.119403970238018</v>
-      </c>
-      <c r="G14">
-        <f>LN(A14/A$2)</f>
-        <v>0.11940397023801684</v>
-      </c>
-      <c r="H14">
-        <f>LN(B14/B$2)</f>
-        <v>0.11940397023801703</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>54.121608000000009</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <f t="shared" si="2"/>
+        <f>A14+H$2*A14</f>
         <v>113.80932804332893</v>
       </c>
       <c r="B15">
-        <f t="shared" si="3"/>
-        <v>341.42798412998684</v>
+        <f>B14+I$2*B14</f>
+        <v>517.4426521815185</v>
       </c>
       <c r="C15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.12935430109118523</v>
       </c>
       <c r="D15">
-        <f t="shared" si="5"/>
-        <v>0.12935430109118523</v>
+        <f t="shared" si="3"/>
+        <v>0.25743415485033655</v>
       </c>
       <c r="E15">
-        <f t="shared" si="6"/>
-        <v>50.129354301091183</v>
+        <f t="shared" si="0"/>
+        <v>52.550502505000004</v>
       </c>
       <c r="F15">
-        <f t="shared" si="7"/>
-        <v>50.129354301091183</v>
-      </c>
-      <c r="G15">
-        <f>LN(A15/A$2)</f>
-        <v>0.12935430109118495</v>
-      </c>
-      <c r="H15">
-        <f>LN(B15/B$2)</f>
-        <v>0.12935430109118515</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <f t="shared" si="1"/>
+        <v>55.204040160000012</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <f t="shared" si="2"/>
+        <f>A15+H$2*A15</f>
         <v>114.94742132376223</v>
       </c>
       <c r="B16">
-        <f t="shared" si="3"/>
-        <v>344.84226397128668</v>
+        <f>B15+I$2*B15</f>
+        <v>527.79150522514885</v>
       </c>
       <c r="C16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.13930463194435333</v>
       </c>
       <c r="D16">
-        <f t="shared" si="5"/>
-        <v>0.13930463194435333</v>
+        <f t="shared" si="3"/>
+        <v>0.27723678214651626</v>
       </c>
       <c r="E16">
-        <f t="shared" si="6"/>
-        <v>50.139304631944356</v>
+        <f t="shared" si="0"/>
+        <v>53.076007530050006</v>
       </c>
       <c r="F16">
-        <f t="shared" si="7"/>
-        <v>50.139304631944356</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>56.308120963200004</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A17">
-        <f t="shared" si="2"/>
+        <f>A16+H$2*A16</f>
         <v>116.09689553699985</v>
       </c>
       <c r="B17">
-        <f t="shared" si="3"/>
-        <v>348.29068661099956</v>
+        <f>B16+I$2*B16</f>
+        <v>538.34733532965186</v>
       </c>
       <c r="C17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.14925496279752143</v>
       </c>
       <c r="D17">
-        <f t="shared" si="5"/>
-        <v>0.14925496279752143</v>
+        <f t="shared" si="3"/>
+        <v>0.29703940944269597</v>
       </c>
       <c r="E17">
-        <f t="shared" si="6"/>
-        <v>50.149254962797521</v>
+        <f t="shared" si="0"/>
+        <v>53.606767605350505</v>
       </c>
       <c r="F17">
-        <f t="shared" si="7"/>
-        <v>50.149254962797521</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>57.434283382464002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18">
-        <f t="shared" si="2"/>
+        <f>A17+H$2*A17</f>
         <v>117.25786449236985</v>
       </c>
       <c r="B18">
-        <f t="shared" si="3"/>
-        <v>351.77359347710956</v>
+        <f>B17+I$2*B17</f>
+        <v>549.11428203624484</v>
       </c>
       <c r="C18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.15920529365068953</v>
       </c>
       <c r="D18">
-        <f t="shared" si="5"/>
-        <v>0.15920529365068953</v>
+        <f t="shared" si="3"/>
+        <v>0.31684203673887568</v>
       </c>
       <c r="E18">
-        <f t="shared" si="6"/>
-        <v>50.159205293650686</v>
+        <f t="shared" si="0"/>
+        <v>54.142835281404011</v>
       </c>
       <c r="F18">
-        <f t="shared" si="7"/>
-        <v>50.159205293650686</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>58.582969050113284</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A19">
-        <f t="shared" si="2"/>
+        <f>A18+H$2*A18</f>
         <v>118.43044313729355</v>
       </c>
       <c r="B19">
-        <f t="shared" si="3"/>
-        <v>355.29132941188067</v>
+        <f>B18+I$2*B18</f>
+        <v>560.0965676769697</v>
       </c>
       <c r="C19">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.16915562450385763</v>
       </c>
       <c r="D19">
-        <f t="shared" si="5"/>
-        <v>0.16915562450385763</v>
+        <f t="shared" si="3"/>
+        <v>0.33664466403505539</v>
       </c>
       <c r="E19">
-        <f t="shared" si="6"/>
-        <v>50.169155624503858</v>
+        <f t="shared" si="0"/>
+        <v>54.684263634218055</v>
       </c>
       <c r="F19">
-        <f t="shared" si="7"/>
-        <v>50.169155624503858</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>59.754628431115556</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A20">
-        <f t="shared" si="2"/>
+        <f>A19+H$2*A19</f>
         <v>119.61474756866649</v>
       </c>
       <c r="B20">
-        <f t="shared" si="3"/>
-        <v>358.84424270599948</v>
+        <f>B19+I$2*B19</f>
+        <v>571.29849903050911</v>
       </c>
       <c r="C20">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.17910595535702573</v>
       </c>
       <c r="D20">
-        <f t="shared" si="5"/>
-        <v>0.17910595535702573</v>
+        <f t="shared" si="3"/>
+        <v>0.35644729133123509</v>
       </c>
       <c r="E20">
-        <f t="shared" si="6"/>
-        <v>50.179105955357024</v>
+        <f t="shared" si="0"/>
+        <v>55.23110627056024</v>
       </c>
       <c r="F20">
-        <f t="shared" si="7"/>
-        <v>50.179105955357024</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>60.949720999737863</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21">
-        <f t="shared" si="2"/>
+        <f>A20+H$2*A20</f>
         <v>120.81089504435315</v>
       </c>
       <c r="B21">
-        <f t="shared" si="3"/>
-        <v>362.43268513305946</v>
+        <f>B20+I$2*B20</f>
+        <v>582.72446901111925</v>
       </c>
       <c r="C21">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.18905628621019382</v>
       </c>
       <c r="D21">
-        <f t="shared" si="5"/>
-        <v>0.18905628621019382</v>
+        <f t="shared" si="3"/>
+        <v>0.3762499186274148</v>
       </c>
       <c r="E21">
-        <f t="shared" si="6"/>
-        <v>50.189056286210196</v>
+        <f t="shared" si="0"/>
+        <v>55.783417333265838</v>
       </c>
       <c r="F21">
-        <f t="shared" si="7"/>
-        <v>50.189056286210196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>62.168715419732621</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22">
-        <f t="shared" si="2"/>
+        <f>A21+H$2*A21</f>
         <v>122.01900399479668</v>
       </c>
       <c r="B22">
-        <f t="shared" si="3"/>
-        <v>366.05701198439004</v>
+        <f>B21+I$2*B21</f>
+        <v>594.3789583913416</v>
       </c>
       <c r="C22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.19900661706336192</v>
       </c>
       <c r="D22">
-        <f t="shared" si="5"/>
-        <v>0.19900661706336192</v>
+        <f t="shared" si="3"/>
+        <v>0.39605254592359451</v>
       </c>
       <c r="E22">
-        <f t="shared" si="6"/>
-        <v>50.199006617063361</v>
+        <f t="shared" si="0"/>
+        <v>56.341251506598496</v>
       </c>
       <c r="F22">
-        <f t="shared" si="7"/>
-        <v>50.199006617063361</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>63.412089728127278</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23">
-        <f t="shared" si="2"/>
+        <f>A22+H$2*A22</f>
         <v>123.23919403474464</v>
       </c>
       <c r="B23">
-        <f t="shared" si="3"/>
-        <v>369.71758210423394</v>
+        <f>B22+I$2*B22</f>
+        <v>606.26653755916846</v>
       </c>
       <c r="C23">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.20895694791653002</v>
       </c>
       <c r="D23">
-        <f t="shared" si="5"/>
-        <v>0.20895694791653002</v>
+        <f t="shared" si="3"/>
+        <v>0.41585517321977422</v>
       </c>
       <c r="E23">
-        <f t="shared" si="6"/>
-        <v>50.208956947916533</v>
+        <f t="shared" si="0"/>
+        <v>56.904664021664487</v>
       </c>
       <c r="F23">
-        <f t="shared" si="7"/>
-        <v>50.208956947916533</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>64.680331522689812</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A24">
-        <f t="shared" si="2"/>
+        <f>A23+H$2*A23</f>
         <v>124.47158597509208</v>
       </c>
       <c r="B24">
-        <f t="shared" si="3"/>
-        <v>373.41475792527626</v>
+        <f>B23+I$2*B23</f>
+        <v>618.39186831035181</v>
       </c>
       <c r="C24">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.21890727876969812</v>
       </c>
       <c r="D24">
-        <f t="shared" si="5"/>
-        <v>0.21890727876969812</v>
+        <f t="shared" si="3"/>
+        <v>0.43565780051595393</v>
       </c>
       <c r="E24">
-        <f t="shared" si="6"/>
-        <v>50.218907278769699</v>
+        <f t="shared" si="0"/>
+        <v>57.473710661881128</v>
       </c>
       <c r="F24">
-        <f t="shared" si="7"/>
-        <v>50.218907278769699</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>65.973938153143607</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25">
-        <f t="shared" si="2"/>
+        <f>A24+H$2*A24</f>
         <v>125.71630183484301</v>
       </c>
       <c r="B25">
-        <f t="shared" si="3"/>
-        <v>377.14890550452901</v>
+        <f>B24+I$2*B24</f>
+        <v>630.75970567655884</v>
       </c>
       <c r="C25">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.22885760962286622</v>
       </c>
       <c r="D25">
-        <f t="shared" si="5"/>
-        <v>0.22885760962286622</v>
+        <f t="shared" si="3"/>
+        <v>0.45546042781213364</v>
       </c>
       <c r="E25">
-        <f t="shared" si="6"/>
-        <v>50.228857609622864</v>
+        <f t="shared" si="0"/>
+        <v>58.048447768499948</v>
       </c>
       <c r="F25">
-        <f t="shared" si="7"/>
-        <v>50.228857609622864</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>67.293416916206482</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26">
-        <f t="shared" si="2"/>
+        <f>A25+H$2*A25</f>
         <v>126.97346485319144</v>
       </c>
       <c r="B26">
-        <f t="shared" si="3"/>
-        <v>380.92039455957428</v>
+        <f>B25+I$2*B25</f>
+        <v>643.37489979009001</v>
       </c>
       <c r="C26">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.23880794047603432</v>
       </c>
       <c r="D26">
-        <f t="shared" si="5"/>
-        <v>0.23880794047603432</v>
+        <f t="shared" si="3"/>
+        <v>0.47526305510831335</v>
       </c>
       <c r="E26">
-        <f t="shared" si="6"/>
-        <v>50.238807940476036</v>
+        <f t="shared" si="0"/>
+        <v>58.628932246184938</v>
       </c>
       <c r="F26">
-        <f t="shared" si="7"/>
-        <v>50.238807940476036</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>68.63928525453062</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27">
-        <f t="shared" si="2"/>
+        <f>A26+H$2*A26</f>
         <v>128.24319950172335</v>
       </c>
       <c r="B27">
-        <f t="shared" si="3"/>
-        <v>384.72959850517003</v>
+        <f>B26+I$2*B26</f>
+        <v>656.24239778589185</v>
       </c>
       <c r="C27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.24875827132920242</v>
       </c>
       <c r="D27">
-        <f t="shared" si="5"/>
-        <v>0.24875827132920242</v>
+        <f t="shared" si="3"/>
+        <v>0.49506568240449306</v>
       </c>
       <c r="E27">
-        <f t="shared" si="6"/>
-        <v>50.248758271329201</v>
+        <f t="shared" si="0"/>
+        <v>59.21522156864679</v>
       </c>
       <c r="F27">
-        <f t="shared" si="7"/>
-        <v>50.248758271329201</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>70.012070959621227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28">
-        <f t="shared" si="2"/>
+        <f>A27+H$2*A27</f>
         <v>129.52563149674057</v>
       </c>
       <c r="B28">
-        <f t="shared" si="3"/>
-        <v>388.57689449022172</v>
+        <f>B27+I$2*B27</f>
+        <v>669.36724574160974</v>
       </c>
       <c r="C28">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.2587086021823703</v>
       </c>
       <c r="D28">
-        <f t="shared" si="5"/>
-        <v>0.25870860218237052</v>
+        <f t="shared" si="3"/>
+        <v>0.51486830970067277</v>
       </c>
       <c r="E28">
-        <f t="shared" si="6"/>
-        <v>50.258708602182374</v>
+        <f t="shared" si="0"/>
+        <v>59.807373784333251</v>
       </c>
       <c r="F28">
-        <f t="shared" si="7"/>
-        <v>50.258708602182374</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>71.412312378813652</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A29">
-        <f t="shared" si="2"/>
+        <f>A28+H$2*A28</f>
         <v>130.82088781170799</v>
       </c>
       <c r="B29">
-        <f t="shared" si="3"/>
-        <v>392.46266343512394</v>
+        <f>B28+I$2*B28</f>
+        <v>682.75459065644191</v>
       </c>
       <c r="C29">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.26865893303553839</v>
       </c>
       <c r="D29">
-        <f t="shared" si="5"/>
-        <v>0.26865893303553862</v>
+        <f t="shared" si="3"/>
+        <v>0.53467093699685253</v>
       </c>
       <c r="E29">
-        <f t="shared" si="6"/>
-        <v>50.268658933035539</v>
+        <f t="shared" si="0"/>
+        <v>60.40544752217658</v>
       </c>
       <c r="F29">
-        <f t="shared" si="7"/>
-        <v>50.268658933035539</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>72.840558626389935</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30">
-        <f t="shared" si="2"/>
+        <f>A29+H$2*A29</f>
         <v>132.12909668982508</v>
       </c>
       <c r="B30">
-        <f t="shared" si="3"/>
-        <v>396.38729006947517</v>
+        <f>B29+I$2*B29</f>
+        <v>696.40968246957073</v>
       </c>
       <c r="C30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.27860926388870649</v>
       </c>
       <c r="D30">
-        <f t="shared" si="5"/>
-        <v>0.27860926388870672</v>
+        <f t="shared" si="3"/>
+        <v>0.55447356429303229</v>
       </c>
       <c r="E30">
-        <f t="shared" si="6"/>
-        <v>50.278609263888704</v>
+        <f t="shared" si="0"/>
+        <v>61.009501997398353</v>
       </c>
       <c r="F30">
-        <f t="shared" si="7"/>
-        <v>50.278609263888704</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>74.297369798917728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31">
-        <f t="shared" si="2"/>
+        <f>A30+H$2*A30</f>
         <v>133.45038765672334</v>
       </c>
       <c r="B31">
-        <f t="shared" si="3"/>
-        <v>400.35116297016992</v>
+        <f>B30+I$2*B30</f>
+        <v>710.33787611896219</v>
       </c>
       <c r="C31">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.28855959474187459</v>
       </c>
       <c r="D31">
-        <f t="shared" si="5"/>
-        <v>0.28855959474187481</v>
+        <f t="shared" si="3"/>
+        <v>0.57427619158921206</v>
       </c>
       <c r="E31">
-        <f t="shared" si="6"/>
-        <v>50.288559594741876</v>
+        <f t="shared" si="0"/>
+        <v>61.619597017372328</v>
       </c>
       <c r="F31">
-        <f t="shared" si="7"/>
-        <v>50.288559594741876</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>75.783317194896085</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32">
-        <f t="shared" si="2"/>
+        <f>A31+H$2*A31</f>
         <v>134.78489153329056</v>
       </c>
       <c r="B32">
-        <f t="shared" si="3"/>
-        <v>404.3546745998716</v>
+        <f>B31+I$2*B31</f>
+        <v>724.54463364134142</v>
       </c>
       <c r="C32">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.29850992559504269</v>
       </c>
       <c r="D32">
-        <f t="shared" si="5"/>
-        <v>0.29850992559504291</v>
+        <f t="shared" si="3"/>
+        <v>0.59407881888539182</v>
       </c>
       <c r="E32">
-        <f t="shared" si="6"/>
-        <v>50.298509925595042</v>
+        <f t="shared" si="0"/>
+        <v>62.235792987546056</v>
       </c>
       <c r="F32">
-        <f t="shared" si="7"/>
-        <v>50.298509925595042</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>77.298983538794005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33">
-        <f t="shared" si="2"/>
+        <f>A32+H$2*A32</f>
         <v>136.13274044862348</v>
       </c>
       <c r="B33">
-        <f t="shared" si="3"/>
-        <v>408.3982213458703</v>
+        <f>B32+I$2*B32</f>
+        <v>739.03552631416824</v>
       </c>
       <c r="C33">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.30846025644821079</v>
       </c>
       <c r="D33">
-        <f t="shared" si="5"/>
-        <v>0.30846025644821101</v>
+        <f t="shared" si="3"/>
+        <v>0.61388144618157159</v>
       </c>
       <c r="E33">
-        <f t="shared" si="6"/>
-        <v>50.308460256448214</v>
+        <f t="shared" si="0"/>
+        <v>62.858150917421518</v>
       </c>
       <c r="F33">
-        <f t="shared" si="7"/>
-        <v>50.308460256448214</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>78.844963209569897</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34">
-        <f t="shared" si="2"/>
+        <f>A33+H$2*A33</f>
         <v>137.49406785310973</v>
       </c>
       <c r="B34">
-        <f t="shared" si="3"/>
-        <v>412.48220355932898</v>
+        <f>B33+I$2*B33</f>
+        <v>753.81623684045155</v>
       </c>
       <c r="C34">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.31841058730137889</v>
       </c>
       <c r="D34">
-        <f t="shared" si="5"/>
-        <v>0.31841058730137911</v>
+        <f t="shared" si="3"/>
+        <v>0.63368407347775135</v>
       </c>
       <c r="E34">
-        <f t="shared" si="6"/>
-        <v>50.318410587301379</v>
+        <f t="shared" si="0"/>
+        <v>63.486732426595736</v>
       </c>
       <c r="F34">
-        <f t="shared" si="7"/>
-        <v>50.318410587301379</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>80.421862473761294</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35">
-        <f t="shared" si="2"/>
+        <f>A34+H$2*A34</f>
         <v>138.86900853164082</v>
       </c>
       <c r="B35">
-        <f t="shared" si="3"/>
-        <v>416.60702559492228</v>
+        <f>B34+I$2*B34</f>
+        <v>768.89256157726061</v>
       </c>
       <c r="C35">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.32836091815454699</v>
       </c>
       <c r="D35">
-        <f t="shared" si="5"/>
-        <v>0.32836091815454721</v>
+        <f t="shared" si="3"/>
+        <v>0.65348670077393112</v>
       </c>
       <c r="E35">
-        <f t="shared" si="6"/>
-        <v>50.328360918154544</v>
+        <f t="shared" si="0"/>
+        <v>64.121599750861691</v>
       </c>
       <c r="F35">
-        <f t="shared" si="7"/>
-        <v>50.328360918154544</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>82.030299723236539</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A36">
-        <f t="shared" si="2"/>
+        <f>A35+H$2*A35</f>
         <v>140.25769861695721</v>
       </c>
       <c r="B36">
-        <f t="shared" si="3"/>
-        <v>420.77309585087153</v>
+        <f>B35+I$2*B35</f>
+        <v>784.27041280880587</v>
       </c>
       <c r="C36">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.33831124900771509</v>
       </c>
       <c r="D36">
-        <f t="shared" si="5"/>
-        <v>0.33831124900771531</v>
+        <f t="shared" si="3"/>
+        <v>0.67328932807011088</v>
       </c>
       <c r="E36">
-        <f t="shared" si="6"/>
-        <v>50.338311249007717</v>
+        <f t="shared" si="0"/>
+        <v>64.762815748370301</v>
       </c>
       <c r="F36">
-        <f t="shared" si="7"/>
-        <v>50.338311249007717</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>83.67090571770126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A37">
-        <f t="shared" si="2"/>
+        <f>A36+H$2*A36</f>
         <v>141.66027560312679</v>
       </c>
       <c r="B37">
-        <f t="shared" si="3"/>
-        <v>424.98082680938023</v>
+        <f>B36+I$2*B36</f>
+        <v>799.95582106498205</v>
       </c>
       <c r="C37">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.34826157986088319</v>
       </c>
       <c r="D37">
-        <f t="shared" si="5"/>
-        <v>0.34826157986088341</v>
+        <f t="shared" si="3"/>
+        <v>0.69309195536629065</v>
       </c>
       <c r="E37">
-        <f t="shared" si="6"/>
-        <v>50.348261579860882</v>
+        <f t="shared" si="0"/>
+        <v>65.410443905854009</v>
       </c>
       <c r="F37">
-        <f t="shared" si="7"/>
-        <v>50.348261579860882</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>85.344323832055295</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A38">
-        <f t="shared" si="2"/>
+        <f>A37+H$2*A37</f>
         <v>143.07687835915806</v>
       </c>
       <c r="B38">
-        <f t="shared" si="3"/>
-        <v>429.23063507747406</v>
+        <f>B37+I$2*B37</f>
+        <v>815.95493748628166</v>
       </c>
       <c r="C38">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.35821191071405128</v>
       </c>
       <c r="D38">
-        <f t="shared" si="5"/>
-        <v>0.35821191071405151</v>
+        <f t="shared" si="3"/>
+        <v>0.71289458266247041</v>
       </c>
       <c r="E38">
-        <f t="shared" si="6"/>
-        <v>50.358211910714054</v>
+        <f t="shared" si="0"/>
+        <v>66.064548344912552</v>
       </c>
       <c r="F38">
-        <f t="shared" si="7"/>
-        <v>50.358211910714054</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>87.051210308696398</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A39">
-        <f t="shared" si="2"/>
+        <f>A38+H$2*A38</f>
         <v>144.50764714274965</v>
       </c>
       <c r="B39">
-        <f t="shared" si="3"/>
-        <v>433.52294142824883</v>
+        <f>B38+I$2*B38</f>
+        <v>832.2740362360073</v>
       </c>
       <c r="C39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.36816224156721938</v>
       </c>
       <c r="D39">
-        <f t="shared" si="5"/>
-        <v>0.36816224156721961</v>
+        <f t="shared" si="3"/>
+        <v>0.73269720995865018</v>
       </c>
       <c r="E39">
-        <f t="shared" si="6"/>
-        <v>50.368162241567219</v>
+        <f t="shared" si="0"/>
+        <v>66.725193828361682</v>
       </c>
       <c r="F39">
-        <f t="shared" si="7"/>
-        <v>50.368162241567219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>88.792234514870344</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A40">
-        <f t="shared" si="2"/>
+        <f>A39+H$2*A39</f>
         <v>145.95272361417713</v>
       </c>
       <c r="B40">
-        <f t="shared" si="3"/>
-        <v>437.85817084253131</v>
+        <f>B39+I$2*B39</f>
+        <v>848.91951696072749</v>
       </c>
       <c r="C40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.37811257242038748</v>
       </c>
       <c r="D40">
-        <f t="shared" si="5"/>
-        <v>0.3781125724203877</v>
+        <f t="shared" si="3"/>
+        <v>0.75249983725482994</v>
       </c>
       <c r="E40">
-        <f t="shared" si="6"/>
-        <v>50.378112572420385</v>
+        <f t="shared" si="0"/>
+        <v>67.392445766645309</v>
       </c>
       <c r="F40">
-        <f t="shared" si="7"/>
-        <v>50.378112572420385</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>90.568079205167749</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A41">
-        <f t="shared" si="2"/>
+        <f>A40+H$2*A40</f>
         <v>147.41225085031891</v>
       </c>
       <c r="B41">
-        <f t="shared" si="3"/>
-        <v>442.23675255095662</v>
+        <f>B40+I$2*B40</f>
+        <v>865.89790729994206</v>
       </c>
       <c r="C41">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.38806290327355558</v>
       </c>
       <c r="D41">
-        <f t="shared" si="5"/>
-        <v>0.3880629032735558</v>
+        <f t="shared" si="3"/>
+        <v>0.7723024645510097</v>
       </c>
       <c r="E41">
-        <f t="shared" si="6"/>
-        <v>50.388062903273557</v>
+        <f t="shared" si="0"/>
+        <v>68.066370224311754</v>
       </c>
       <c r="F41">
-        <f t="shared" si="7"/>
-        <v>50.388062903273557</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>92.379440789271101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A42">
-        <f t="shared" si="2"/>
+        <f>A41+H$2*A41</f>
         <v>148.88637335882211</v>
       </c>
       <c r="B42">
-        <f t="shared" si="3"/>
-        <v>446.65912007646619</v>
+        <f>B41+I$2*B41</f>
+        <v>883.21586544594095</v>
       </c>
       <c r="C42">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.39801323412672368</v>
       </c>
       <c r="D42">
-        <f t="shared" si="5"/>
-        <v>0.3980132341267239</v>
+        <f t="shared" si="3"/>
+        <v>0.79210509184718947</v>
       </c>
       <c r="E42">
-        <f t="shared" si="6"/>
-        <v>50.398013234126722</v>
+        <f t="shared" si="0"/>
+        <v>68.747033926554863</v>
       </c>
       <c r="F42">
-        <f t="shared" si="7"/>
-        <v>50.398013234126722</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>94.227029605056529</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A43">
-        <f t="shared" si="2"/>
+        <f>A42+H$2*A42</f>
         <v>150.37523709241034</v>
       </c>
       <c r="B43">
-        <f t="shared" si="3"/>
-        <v>451.12571127723083</v>
+        <f>B42+I$2*B42</f>
+        <v>900.88018275485979</v>
       </c>
       <c r="C43">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.40796356497989178</v>
       </c>
       <c r="D43">
-        <f t="shared" si="5"/>
-        <v>0.407963564979892</v>
+        <f t="shared" si="3"/>
+        <v>0.81190771914336923</v>
       </c>
       <c r="E43">
-        <f t="shared" si="6"/>
-        <v>50.407963564979894</v>
+        <f t="shared" si="0"/>
+        <v>69.434504265820422</v>
       </c>
       <c r="F43">
-        <f t="shared" si="7"/>
-        <v>50.407963564979894</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>96.111570197157675</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44">
-        <f t="shared" si="2"/>
+        <f>A43+H$2*A43</f>
         <v>151.87898946333445</v>
       </c>
       <c r="B44">
-        <f t="shared" si="3"/>
-        <v>455.63696839000312</v>
+        <f>B43+I$2*B43</f>
+        <v>918.89778640995701</v>
       </c>
       <c r="C44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.41791389583305988</v>
       </c>
       <c r="D44">
-        <f t="shared" si="5"/>
-        <v>0.4179138958330601</v>
+        <f t="shared" si="3"/>
+        <v>0.831710346439549</v>
       </c>
       <c r="E44">
-        <f t="shared" si="6"/>
-        <v>50.41791389583306</v>
+        <f t="shared" si="0"/>
+        <v>70.128849308478621</v>
       </c>
       <c r="F44">
-        <f t="shared" si="7"/>
-        <v>50.41791389583306</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>98.033801601100819</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A45">
-        <f t="shared" si="2"/>
+        <f>A44+H$2*A44</f>
         <v>153.39777935796781</v>
       </c>
       <c r="B45">
-        <f t="shared" si="3"/>
-        <v>460.19333807390313</v>
+        <f>B44+I$2*B44</f>
+        <v>937.27574213815615</v>
       </c>
       <c r="C45">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.42786422668622798</v>
       </c>
       <c r="D45">
-        <f t="shared" si="5"/>
-        <v>0.4278642266862282</v>
+        <f t="shared" si="3"/>
+        <v>0.85151297373572876</v>
       </c>
       <c r="E45">
-        <f t="shared" si="6"/>
-        <v>50.427864226686225</v>
+        <f t="shared" si="0"/>
+        <v>70.830137801563424</v>
       </c>
       <c r="F45">
-        <f t="shared" si="7"/>
-        <v>50.427864226686225</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>99.994477633122841</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A46">
-        <f t="shared" si="2"/>
+        <f>A45+H$2*A45</f>
         <v>154.93175715154749</v>
       </c>
       <c r="B46">
-        <f t="shared" si="3"/>
-        <v>464.79527145464215</v>
+        <f>B45+I$2*B45</f>
+        <v>956.02125698091925</v>
       </c>
       <c r="C46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.43781455753939608</v>
       </c>
       <c r="D46">
-        <f t="shared" si="5"/>
-        <v>0.4378145575393963</v>
+        <f t="shared" si="3"/>
+        <v>0.87131560103190853</v>
       </c>
       <c r="E46">
-        <f t="shared" si="6"/>
-        <v>50.437814557539397</v>
+        <f t="shared" si="0"/>
+        <v>71.538439179579044</v>
       </c>
       <c r="F46">
-        <f t="shared" si="7"/>
-        <v>50.437814557539397</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>101.99436718578532</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A47">
-        <f t="shared" si="2"/>
+        <f>A46+H$2*A46</f>
         <v>156.48107472306296</v>
       </c>
       <c r="B47">
-        <f t="shared" si="3"/>
-        <v>469.44322416918857</v>
+        <f>B46+I$2*B46</f>
+        <v>975.14168212053767</v>
       </c>
       <c r="C47">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.44776488839256418</v>
       </c>
       <c r="D47">
-        <f t="shared" si="5"/>
-        <v>0.4477648883925644</v>
+        <f t="shared" si="3"/>
+        <v>0.89111822832808829</v>
       </c>
       <c r="E47">
-        <f t="shared" si="6"/>
-        <v>50.447764888392562</v>
+        <f t="shared" si="0"/>
+        <v>72.253823571374838</v>
       </c>
       <c r="F47">
-        <f t="shared" si="7"/>
-        <v>50.447764888392562</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>104.03425452950101</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A48">
-        <f t="shared" si="2"/>
+        <f>A47+H$2*A47</f>
         <v>158.0458854702936</v>
       </c>
       <c r="B48">
-        <f t="shared" si="3"/>
-        <v>474.13765641088048</v>
+        <f>B47+I$2*B47</f>
+        <v>994.64451576294846</v>
       </c>
       <c r="C48">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.45771521924573227</v>
       </c>
       <c r="D48">
-        <f t="shared" si="5"/>
-        <v>0.4577152192457325</v>
+        <f t="shared" si="3"/>
+        <v>0.91092085562426806</v>
       </c>
       <c r="E48">
-        <f t="shared" si="6"/>
-        <v>50.457715219245735</v>
+        <f t="shared" si="0"/>
+        <v>72.976361807088594</v>
       </c>
       <c r="F48">
-        <f t="shared" si="7"/>
-        <v>50.457715219245735</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>106.11493962009104</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A49">
-        <f t="shared" si="2"/>
+        <f>A48+H$2*A48</f>
         <v>159.62634432499652</v>
       </c>
       <c r="B49">
-        <f t="shared" si="3"/>
-        <v>478.87903297498929</v>
+        <f>B48+I$2*B48</f>
+        <v>1014.5374060782075</v>
       </c>
       <c r="C49">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.46766555009890037</v>
       </c>
       <c r="D49">
-        <f t="shared" si="5"/>
-        <v>0.4676655500989006</v>
+        <f t="shared" si="3"/>
+        <v>0.93072348292044782</v>
       </c>
       <c r="E49">
-        <f t="shared" si="6"/>
-        <v>50.4676655500989</v>
+        <f t="shared" si="0"/>
+        <v>73.70612542515947</v>
       </c>
       <c r="F49">
-        <f t="shared" si="7"/>
-        <v>50.4676655500989</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <f t="shared" si="1"/>
+        <v>108.23723841249289</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A50">
-        <f t="shared" si="2"/>
+        <f>A49+H$2*A49</f>
         <v>161.22260776824649</v>
       </c>
       <c r="B50">
-        <f t="shared" si="3"/>
-        <v>483.66782330473916</v>
+        <f>B49+I$2*B49</f>
+        <v>1034.8281541997717</v>
       </c>
       <c r="C50">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>0.47761588095206847</v>
       </c>
       <c r="D50">
-        <f t="shared" si="5"/>
-        <v>0.47761588095206869</v>
+        <f t="shared" si="3"/>
+        <v>0.95052611021662758</v>
       </c>
       <c r="E50">
-        <f t="shared" si="6"/>
-        <v>50.477615880952065</v>
+        <f t="shared" si="0"/>
+        <v>74.44318667941107</v>
       </c>
       <c r="F50">
-        <f t="shared" si="7"/>
-        <v>50.477615880952065</v>
+        <f t="shared" si="1"/>
+        <v>110.40198318074275</v>
       </c>
     </row>
   </sheetData>
